--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488229_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488229_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. DIAZ MACIAS</t>
+          <t>M. RAMOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8555</v>
+        <v>1.2662</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7141</v>
+        <v>1.2662</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8586</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3906</v>
+        <v>1.2662</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0542</v>
+        <v>0.6441</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6635</v>
+        <v>0.6221</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4877</v>
+        <v>1.2662</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1393</v>
+        <v>0.6441</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3484</v>
+        <v>0.6221</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.0971</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0851</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.012</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0001</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1741</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8259</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.503</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9433</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RAMOS RODRÍGUEZ</t>
+          <t>A. DIAZ MACIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2662</v>
+        <v>0.6294</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2662</v>
+        <v>1.8328</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1.2033</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2662</v>
+        <v>2.3906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6441</v>
+        <v>3.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6221</v>
+        <v>-0.6635</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2662</v>
+        <v>5.4877</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6441</v>
+        <v>4.1393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6221</v>
+        <v>1.3484</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-3.0971</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-1.0851</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-2.012</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.891</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.226</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.4812</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.9433</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.4403</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NAVARRO GARRIDO</t>
+          <t>F. COTAN MOYA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6139</v>
+        <v>0.2682</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0506</v>
+        <v>1.5117</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5632</v>
+        <v>-1.2435</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3583</v>
+        <v>-2.7982</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9372</v>
+        <v>-1.1513</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.579</v>
+        <v>-1.6469</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6351</v>
+        <v>0.2295</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4692</v>
+        <v>0.2791</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1659</v>
+        <v>-0.0497</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.2768</v>
+        <v>-3.0277</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.532</v>
+        <v>-1.4304</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7448</v>
+        <v>-1.5973</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3706</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0272</v>
+        <v>-0.5282</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2584</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2313</v>
+        <v>0.2425</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3155</v>
+        <v>3.9651</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3155</v>
+        <v>4.091</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. COTAN MOYA</t>
+          <t>S. NAVARRO GARRIDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6389</v>
+        <v>-0.07389999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8262</v>
+        <v>0.2432</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4651</v>
+        <v>-0.317</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7982</v>
+        <v>0.3583</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1513</v>
+        <v>0.9372</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6469</v>
+        <v>-0.579</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2295</v>
+        <v>2.6351</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2791</v>
+        <v>2.4692</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0497</v>
+        <v>0.1659</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0277</v>
+        <v>-2.2768</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4304</v>
+        <v>-1.532</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5973</v>
+        <v>-0.7448</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3706</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4353</v>
+        <v>-0.4871</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4562</v>
+        <v>-0.9647</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0209</v>
+        <v>0.4775</v>
       </c>
       <c r="V5" t="n">
-        <v>3.9651</v>
+        <v>-0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>4.091</v>
+        <v>-0.3155</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0488</v>
+        <v>-2.1966</v>
       </c>
       <c r="E6" t="n">
         <v>-0.5982</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4506</v>
+        <v>-1.5983</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1706</v>
@@ -922,13 +922,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1196</v>
+        <v>-0.2674</v>
       </c>
       <c r="T6" t="n">
         <v>-0.4377</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3181</v>
+        <v>0.1704</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3144</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LLANO ABASCAL</t>
+          <t>J. VIOQUE LOMBARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.447</v>
+        <v>-2.5797</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8293</v>
+        <v>-1.9111</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6177</v>
+        <v>-0.6686</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0177</v>
+        <v>-0.3657</v>
       </c>
       <c r="H7" t="n">
-        <v>0.231</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2487</v>
+        <v>-0.2903</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4968</v>
+        <v>-0.099</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4554</v>
+        <v>0.4294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0415</v>
+        <v>-0.5284</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5145</v>
+        <v>-0.2667</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2244</v>
+        <v>-0.5048</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2901</v>
+        <v>0.2381</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.0382</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8819</v>
+        <v>-0.3252</v>
       </c>
       <c r="T7" t="n">
-        <v>0.342</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5399</v>
+        <v>0.245</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3847</v>
+        <v>-1.8888</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.63</v>
+        <v>-0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7548</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5537</v>
+        <v>-2.6018</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1607</v>
+        <v>-1.3566</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3929</v>
+        <v>-1.2452</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4264</v>
@@ -1078,13 +1078,13 @@
         <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0569</v>
+        <v>-0.1051</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0037</v>
+        <v>-0.1996</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0532</v>
+        <v>0.0945</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0703</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VIOQUE LOMBARDO</t>
+          <t>A. LLANO ABASCAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0464</v>
+        <v>-3.2813</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.107</v>
+        <v>-1.319</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9394</v>
+        <v>-1.9624</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3657</v>
+        <v>-1.0177</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.231</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2903</v>
+        <v>-1.2487</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.099</v>
+        <v>1.4968</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4294</v>
+        <v>1.4554</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5284</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2667</v>
+        <v>-2.5145</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5048</v>
+        <v>-1.2244</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2381</v>
+        <v>-1.2901</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7919</v>
+        <v>0.0476</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.766</v>
+        <v>-0.1476</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0259</v>
+        <v>0.1952</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8888</v>
+        <v>-1.3847</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3155</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5733</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9906</v>
+        <v>-3.8932</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1877</v>
+        <v>-3.9918</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1971</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8502</v>
@@ -1234,13 +1234,13 @@
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6974</v>
+        <v>-0.6</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8542999999999999</v>
+        <v>-0.6584</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1569</v>
+        <v>0.0584</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6283</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4398</v>
+        <v>-5.9496</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5879</v>
+        <v>-4.1962</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8519</v>
+        <v>-1.7534</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1051</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5238</v>
+        <v>-0.0336</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.526</v>
+        <v>-0.1343</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0022</v>
+        <v>0.1007</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6992</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5231</v>
+        <v>-6.7682</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1983</v>
+        <v>-3.3941</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3248</v>
+        <v>-3.374</v>
       </c>
       <c r="G12" t="n">
         <v>-6.019</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1335</v>
+        <v>-0.3786</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3867</v>
+        <v>-0.5826</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2532</v>
+        <v>0.2039</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1426,7 +1426,7 @@
         <v>-25.1805</v>
       </c>
       <c r="E13" t="n">
-        <v>-11.9132</v>
+        <v>-11.9131</v>
       </c>
       <c r="F13" t="n">
         <v>-13.2671</v>
@@ -1477,7 +1477,7 @@
         <v>2.2693</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.833100000000001</v>
+        <v>-2.8331</v>
       </c>
       <c r="W13" t="n">
         <v>5.3466</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.7897</v>
+        <v>9.385899999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5766</v>
+        <v>5.9684</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2131</v>
+        <v>3.4175</v>
       </c>
       <c r="G14" t="n">
         <v>4.7298</v>
@@ -1546,13 +1546,13 @@
         <v>1.1117</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1995</v>
+        <v>0.3967</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4166</v>
+        <v>-0.0249</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2171</v>
+        <v>0.4215</v>
       </c>
       <c r="V14" t="n">
         <v>3.1477</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8625</v>
+        <v>5.9685</v>
       </c>
       <c r="E15" t="n">
         <v>5.0086</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8539</v>
+        <v>0.9599</v>
       </c>
       <c r="G15" t="n">
         <v>3.7759</v>
@@ -1624,13 +1624,13 @@
         <v>1.1117</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3454</v>
+        <v>0.4514</v>
       </c>
       <c r="T15" t="n">
         <v>-0.092</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4375</v>
+        <v>0.5434</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5543</v>
+        <v>5.6522</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1704</v>
+        <v>4.2683</v>
       </c>
       <c r="F16" t="n">
         <v>1.3839</v>
@@ -1702,10 +1702,10 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0124</v>
+        <v>0.1104</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6901</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="U16" t="n">
         <v>0.7026</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4917</v>
+        <v>4.3727</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9638</v>
+        <v>3.8866</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5279</v>
+        <v>0.4861</v>
       </c>
       <c r="G17" t="n">
         <v>1.5013</v>
@@ -1780,13 +1780,13 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9904</v>
+        <v>0.8714</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3779</v>
+        <v>0.3006</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6125</v>
+        <v>0.5708</v>
       </c>
       <c r="V17" t="n">
         <v>1.2589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9259</v>
+        <v>2.1351</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9346</v>
+        <v>-0.1163</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.008699999999999999</v>
+        <v>2.2514</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3727</v>
+        <v>1.6303</v>
       </c>
       <c r="H19" t="n">
-        <v>0.585</v>
+        <v>1.1972</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7878</v>
+        <v>0.4332</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3176</v>
+        <v>1.1835</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0521</v>
+        <v>1.142</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2655</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="N19" t="n">
         <v>0.0552</v>
       </c>
-      <c r="N19" t="n">
-        <v>-0.4671</v>
-      </c>
       <c r="O19" t="n">
-        <v>0.5223</v>
+        <v>0.3917</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1743</v>
+        <v>0.078</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.383</v>
+        <v>-0.3734</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2087</v>
+        <v>0.4514</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3842</v>
+        <v>-0.3144</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3842</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7663</v>
+        <v>2.0244</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2142</v>
+        <v>1.9346</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9806</v>
+        <v>0.0898</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6303</v>
+        <v>2.3727</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1972</v>
+        <v>0.585</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4332</v>
+        <v>1.7878</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1835</v>
+        <v>2.3176</v>
       </c>
       <c r="K20" t="n">
-        <v>1.142</v>
+        <v>1.0521</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0415</v>
+        <v>1.2655</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4469</v>
+        <v>0.0552</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0552</v>
+        <v>-0.4671</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3917</v>
+        <v>0.5223</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6676</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2907</v>
+        <v>-0.0759</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4713</v>
+        <v>-0.383</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1806</v>
+        <v>0.3071</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3144</v>
+        <v>-1.3842</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3144</v>
+        <v>-1.3842</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3627</v>
+        <v>0.5104</v>
       </c>
       <c r="E21" t="n">
         <v>-1.7079</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0706</v>
+        <v>2.2183</v>
       </c>
       <c r="G21" t="n">
         <v>-0.318</v>
@@ -2092,13 +2092,13 @@
         <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1204</v>
+        <v>0.0274</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3619</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2415</v>
+        <v>0.3892</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1253</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. YOUNG MEDIERO</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0036</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6841</v>
+        <v>-0.7381</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6877</v>
+        <v>1.2386</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1541</v>
+        <v>1.284</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1486</v>
+        <v>0.8032</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3026</v>
+        <v>0.4808</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4065</v>
+        <v>0.9208</v>
       </c>
       <c r="K22" t="n">
-        <v>0.365</v>
+        <v>0.7857</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>0.1351</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2524</v>
+        <v>0.3632</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5135999999999999</v>
+        <v>0.0174</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2611</v>
+        <v>0.3457</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3454</v>
+        <v>0.3283</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1641</v>
+        <v>0.194</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.1343</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1253</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>A. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4157</v>
+        <v>-0.2672</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1298</v>
+        <v>-0.6841</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7141</v>
+        <v>0.4169</v>
       </c>
       <c r="G23" t="n">
-        <v>1.284</v>
+        <v>0.1541</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8032</v>
+        <v>-0.1486</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4808</v>
+        <v>0.3026</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9208</v>
+        <v>0.4065</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7857</v>
+        <v>0.365</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1351</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3632</v>
+        <v>-0.2524</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0174</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3457</v>
+        <v>0.2611</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1117</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5879</v>
+        <v>0.0746</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1977</v>
+        <v>-0.1641</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3902</v>
+        <v>0.2388</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.1253</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.1253</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4384</v>
+        <v>-1.4882</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1574</v>
+        <v>-2.0594</v>
       </c>
       <c r="F24" t="n">
-        <v>0.719</v>
+        <v>0.5713</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5569</v>
@@ -2326,13 +2326,13 @@
         <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3392</v>
+        <v>0.2894</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.526</v>
+        <v>-0.4281</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8652</v>
+        <v>0.7175</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5177</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9604</v>
+        <v>-2.1182</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8325</v>
+        <v>-1.7733</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8721</v>
+        <v>-0.3449</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6053</v>
+        <v>-1.3374</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6086</v>
+        <v>-1.2006</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0033</v>
+        <v>-0.1367</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8637</v>
+        <v>-0.4183</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1125</v>
+        <v>-0.4811</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2488</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7417</v>
+        <v>-0.9191</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.4961</v>
+        <v>-0.7196</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.2456</v>
+        <v>-0.1996</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0382</v>
+        <v>0.1853</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3686</v>
+        <v>0.1041</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1816</v>
+        <v>-0.4281</v>
       </c>
       <c r="U25" t="n">
-        <v>1.187</v>
+        <v>0.5322</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3144</v>
+        <v>-1.0703</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6289</v>
+        <v>-0.0005</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3144</v>
+        <v>-1.0697</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.3639</v>
+        <v>-2.4695</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8712</v>
+        <v>-2.9304</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.4927</v>
+        <v>0.461</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.3374</v>
+        <v>-1.6053</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.2006</v>
+        <v>-1.6086</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1367</v>
+        <v>0.0033</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4183</v>
+        <v>-0.8637</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4811</v>
+        <v>-1.1125</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.2488</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9191</v>
+        <v>-0.7417</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7196</v>
+        <v>-0.4961</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1996</v>
+        <v>-0.2456</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1415</v>
+        <v>0.8596</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.526</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3845</v>
+        <v>0.7759</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.0703</v>
+        <v>0.3144</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.0005</v>
+        <v>0.6289</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.0697</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>25.7886</v>
+        <v>26.41689999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>13.2672</v>
+        <v>13.2673</v>
       </c>
       <c r="F27" t="n">
-        <v>12.5215</v>
+        <v>13.1498</v>
       </c>
       <c r="G27" t="n">
         <v>15.6072</v>
@@ -2560,13 +2560,13 @@
         <v>14.8228</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8871</v>
+        <v>3.5154</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.2692</v>
+        <v>-2.2695</v>
       </c>
       <c r="U27" t="n">
-        <v>5.1566</v>
+        <v>5.784700000000001</v>
       </c>
       <c r="V27" t="n">
         <v>3.588699999999998</v>
